--- a/output/2026-10-03_17_Malesia_Perak_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-03_17_Malesia_Perak_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -475,7 +475,6 @@
           <t>Asia-Mech Hydro-Pneumatic (M) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Ipoh, Perak</t>
@@ -491,10 +490,9 @@
           <t>605-282 1518</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trader dal 1993, distributore sistemi elettro-pneumatici/idraulici (marchi ASR Hydraulic, CNF System, ASR Pneumatic). Sede: Jalan Lahat, Falim, Ipoh.</t>
+          <t>Trader dal 1993, distributore sistemi elettro-pneumatici/idraulici (marchi ASR Hydraulic, CNF System, ASR Pneumatic). Sede: Jalan Lahat, Falim, Ipoh. [DUPLICATO — vedi anche: 2026-10-03_11_Malesia_Perak_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -509,7 +507,6 @@
           <t>Wah Seng Sin Kee Co Sdn Bhd</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Ipoh, Perak</t>
@@ -520,11 +517,9 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Grossista storico hardware industriale dal 1950, multi-filiale (KL, Kuantan, Butterworth). Sede: Jalan Menglembu, Ipoh. Telefono/email non reperiti pubblicamente.</t>
+          <t>Grossista storico hardware industriale dal 1950, multi-filiale (KL, Kuantan, Butterworth). Sede: Jalan Menglembu, Ipoh. Telefono/email non reperiti pubblicamente. [DUPLICATO — vedi anche: 2026-10-03_11_Malesia_Perak_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -539,7 +534,6 @@
           <t>LK Fastener Hardware</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Ipoh, Perak</t>
@@ -555,7 +549,6 @@
           <t>+60 16-526 9892</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Fornitore fasteners/utensili/hardware, reg. societaria 53423321W. Nota: in alcune fonti indirizzo legale risulta Singapore - da approfondire in verifica umana.</t>
@@ -573,7 +566,6 @@
           <t>Madsungai Workshop</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Ipoh, Perak</t>
@@ -589,7 +581,6 @@
           <t>017-511 3532</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Bearing supplier con attivita' aggiuntive di ingegneria/automazione, rating 4.8/5 su directory. Sede: Kawasan Perindustrian IGB, Persiaran Klebang 1, Ipoh. ATTENZIONE: nome 'Workshop' + presenza in directory 'machine maintenance' - verificare umanamente se e' prevalentemente distributore o officina/servizio.</t>
@@ -627,7 +618,6 @@
           <t>05-254 4333</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Distributore regionale consolidato (gruppo SLS Bearings, dal 1963/1972), partner SKF/Timken/INA/Enerpac/Tsubaki/Siemens. Sede: Medan Bendahara 1, Taman Taiping, Ipoh.</t>
@@ -635,7 +625,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -645,7 +635,6 @@
           <t>Zhongyang Engineering Sdn Bhd</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Pusing, Perak</t>
@@ -656,8 +645,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Dealer/rivenditore macchine utensili per metalworking (torni, fresatrici, presse piegatrici, cesoie, rettificatrici, saldatrici), tra i maggiori dealer macchinari in SE Asia.</t>
